--- a/data/raw/Kawak/2024.xlsx
+++ b/data/raw/Kawak/2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92F5AAB6-525B-4578-9C13-2D9201593648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{92F5AAB6-525B-4578-9C13-2D9201593648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98149F11-0E3C-40B7-9ECD-BCBC74E4ECEF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5519CFF8-8A1E-4796-BD21-1D156480F993}"/>
   </bookViews>
@@ -19,17 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$U$316</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1224,7 +1213,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1236,6 +1225,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1324,7 +1314,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{648AEA92-AA47-446F-92F3-BDEF08EB3BFF}"/>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -21703,6 +21695,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:U316" xr:uid="{E2A84CA1-27DD-408B-9CE7-BDC104949C50}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
